--- a/SGC-CKN/Excel/612ab3ca-aad1-48eb-9890-48cd196766a4_Thi_công_cọc_khoan_nhồi_P1-73_D800_28-03-2026.xlsx
+++ b/SGC-CKN/Excel/612ab3ca-aad1-48eb-9890-48cd196766a4_Thi_công_cọc_khoan_nhồi_P1-73_D800_28-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
   <si>
     <t>Dự án</t>
   </si>
@@ -99,7 +99,7 @@
 27/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">22:55
+    <t xml:space="preserve">22:35
 27/03/2026</t>
   </si>
   <si>
@@ -174,6 +174,9 @@
   <si>
     <t xml:space="preserve">06:34
 28/03/2026</t>
+  </si>
+  <si>
+    <t>NT chạm sỏi CĐ: 34,96</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -328,7 +331,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -338,12 +341,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7F3D0"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -504,17 +507,17 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1162,13 +1165,13 @@
         <v>-1.7</v>
       </c>
       <c r="H11" s="5">
-        <v>0.58</v>
+        <v>0.25</v>
       </c>
       <c r="I11" s="5">
         <v>1.7</v>
       </c>
       <c r="J11" s="8">
-        <v>2.91</v>
+        <v>6.8</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>29</v>
@@ -1197,50 +1200,50 @@
         <v>-4.8</v>
       </c>
       <c r="H12" s="9">
-        <v>0.08</v>
+        <v>0.42</v>
       </c>
       <c r="I12" s="9">
         <v>3.1</v>
       </c>
-      <c r="J12" s="12">
-        <v>37.2</v>
+      <c r="J12" s="8">
+        <v>7.44</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>-4.8</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>-8.2</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <v>1</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <v>3.4</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="15">
         <v>3.4</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="13" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1272,7 +1275,7 @@
       <c r="I14" s="16">
         <v>8.8</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="15">
         <v>4.4</v>
       </c>
       <c r="K14" s="17" t="s">
@@ -1307,7 +1310,7 @@
       <c r="I15" s="19">
         <v>5.2</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="8">
         <v>7.8</v>
       </c>
       <c r="K15" s="20" t="s">
@@ -1342,7 +1345,7 @@
       <c r="I16" s="22">
         <v>4</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="8">
         <v>9.6</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -1377,7 +1380,7 @@
       <c r="I17" s="25">
         <v>12.5</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="8">
         <v>8.93</v>
       </c>
       <c r="K17" s="26" t="s">
@@ -1416,12 +1419,12 @@
         <v>0.6</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
@@ -1527,31 +1530,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1574,13 +1577,13 @@
         <v>-1.7</v>
       </c>
       <c r="G2" s="5">
-        <v>0.58</v>
+        <v>0.25</v>
       </c>
       <c r="H2" s="5">
         <v>1.7</v>
       </c>
       <c r="I2" s="8">
-        <v>2.91</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1603,41 +1606,41 @@
         <v>-4.8</v>
       </c>
       <c r="G3" s="9">
-        <v>0.08</v>
+        <v>0.42</v>
       </c>
       <c r="H3" s="9">
         <v>3.1</v>
       </c>
-      <c r="I3" s="12">
-        <v>37.2</v>
+      <c r="I3" s="8">
+        <v>7.44</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>-4.8</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>-8.2</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>1</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>3.4</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="15">
         <v>3.4</v>
       </c>
     </row>
@@ -1666,7 +1669,7 @@
       <c r="H5" s="16">
         <v>8.8</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="15">
         <v>4.4</v>
       </c>
     </row>
@@ -1695,7 +1698,7 @@
       <c r="H6" s="19">
         <v>5.2</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="8">
         <v>7.8</v>
       </c>
     </row>
@@ -1724,7 +1727,7 @@
       <c r="H7" s="22">
         <v>4</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="8">
         <v>9.6</v>
       </c>
     </row>
@@ -1753,7 +1756,7 @@
       <c r="H8" s="25">
         <v>12.5</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="8">
         <v>8.93</v>
       </c>
     </row>
@@ -1788,7 +1791,7 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>29</v>
